--- a/data/trans_dic/P25C_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,87</t>
+          <t>0,41; 4,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,68</t>
+          <t>0,58; 3,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,06; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 10,61</t>
+          <t>2,43; 10,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,17</t>
+          <t>0,31; 4,32</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,28</t>
+          <t>0,44; 5,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,05</t>
+          <t>0,87; 9,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,96</t>
+          <t>1,01; 5,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,17</t>
+          <t>1,2; 5,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,02</t>
+          <t>2,02; 8,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,41</t>
+          <t>2,0; 5,3</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,84</t>
+          <t>0,64; 2,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,87</t>
+          <t>2,36; 5,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,32</t>
+          <t>1,12; 3,33</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>518; 5580</t>
+          <t>472; 5459</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 2602</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>891; 6021</t>
+          <t>951; 6097</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 12782</t>
+          <t>253; 13393</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2190; 8846</t>
+          <t>2029; 8588</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1606; 20112</t>
+          <t>1501; 20857</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>609; 7472</t>
+          <t>621; 7306</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668; 7522</t>
+          <t>650; 6862</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1900; 10732</t>
+          <t>2177; 11199</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2164; 10072</t>
+          <t>2338; 10816</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2981; 10436</t>
+          <t>2629; 10520</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6853; 17565</t>
+          <t>6487; 17227</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4998; 24125</t>
+          <t>5471; 23595</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8274; 19798</t>
+          <t>7949; 19165</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13092; 39386</t>
+          <t>13243; 39568</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,77</t>
+          <t>0,58; 5,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,72</t>
+          <t>0,54; 4,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,36</t>
+          <t>0,95; 5,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,3</t>
+          <t>2,51; 10,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,32</t>
+          <t>1,82; 5,56</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,17</t>
+          <t>0,42; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,17</t>
+          <t>0,87; 9,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,18</t>
+          <t>1,0; 5,09</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,55</t>
+          <t>1,06; 5,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,09</t>
+          <t>1,95; 8,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,3</t>
+          <t>1,85; 5,11</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,78</t>
+          <t>1,4; 3,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,68</t>
+          <t>2,51; 5,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,33</t>
+          <t>2,11; 3,91</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>565</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3149</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>472; 5459</t>
+          <t>710; 6834</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2602</t>
+          <t>0; 2372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>951; 6097</t>
+          <t>949; 7151</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8986</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>253; 13393</t>
+          <t>1622; 9277</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2029; 8588</t>
+          <t>2261; 9204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1501; 20857</t>
+          <t>4755; 14511</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5933</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>621; 7306</t>
+          <t>691; 8079</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>650; 6862</t>
+          <t>726; 7541</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2177; 11199</t>
+          <t>2471; 12636</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11393</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2338; 10816</t>
+          <t>2144; 10905</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2629; 10520</t>
+          <t>2718; 11272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6487; 17227</t>
+          <t>6297; 17420</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5471; 23595</t>
+          <t>9227; 23473</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7949; 19165</t>
+          <t>9192; 21380</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13243; 39568</t>
+          <t>21661; 40124</t>
         </is>
       </c>
     </row>
